--- a/results/greedy/UAVs5_GRID13/revenue/UAVs5_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs5_GRID13/revenue/UAVs5_GRID13_Greedy.xlsx
@@ -557,7 +557,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02371833298821002</v>
+        <v>0.02296962501714006</v>
       </c>
       <c r="C2" t="n">
         <v>20.45781421728963</v>
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02832600002875552</v>
+        <v>0.02785950002726167</v>
       </c>
       <c r="C2" t="n">
         <v>24.21082778502821</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02761345799081028</v>
+        <v>0.02710983296856284</v>
       </c>
       <c r="C2" t="n">
         <v>26.87304175582018</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03124062501592562</v>
+        <v>0.03039020899450406</v>
       </c>
       <c r="C2" t="n">
         <v>21.98602605756687</v>
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04739941697334871</v>
+        <v>0.04430641699582338</v>
       </c>
       <c r="C2" t="n">
         <v>30.64303103957917</v>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03436895797494799</v>
+        <v>0.03335133299697191</v>
       </c>
       <c r="C2" t="n">
         <v>29.67441391729876</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0312752079917118</v>
+        <v>0.02997954201418906</v>
       </c>
       <c r="C2" t="n">
         <v>24.79311739002188</v>
@@ -1075,7 +1075,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03481470898259431</v>
+        <v>0.03344879200449213</v>
       </c>
       <c r="C2" t="n">
         <v>26.0120082395282</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02677362499525771</v>
+        <v>0.0259322079946287</v>
       </c>
       <c r="C2" t="n">
         <v>24.10598692034544</v>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02609362499788404</v>
+        <v>0.02525433403206989</v>
       </c>
       <c r="C2" t="n">
         <v>27.54208785664958</v>
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02898791700135916</v>
+        <v>0.02852349996101111</v>
       </c>
       <c r="C2" t="n">
         <v>32.12246092247315</v>
@@ -1371,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03028775000711903</v>
+        <v>0.0293934170040302</v>
       </c>
       <c r="C2" t="n">
         <v>24.53157304962176</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02800141600891948</v>
+        <v>0.02698595798574388</v>
       </c>
       <c r="C2" t="n">
         <v>21.37485198136912</v>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03607129195006564</v>
+        <v>0.03562583401799202</v>
       </c>
       <c r="C2" t="n">
         <v>26.02678542891199</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02927362499758601</v>
+        <v>0.02830870798788965</v>
       </c>
       <c r="C2" t="n">
         <v>20.35028790612021</v>
@@ -1667,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02787758299382403</v>
+        <v>0.02691191696794704</v>
       </c>
       <c r="C2" t="n">
         <v>21.64598371852564</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03403575002448633</v>
+        <v>0.0337352910428308</v>
       </c>
       <c r="C2" t="n">
         <v>24.87876843618622</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02455037500476465</v>
+        <v>0.02387729199836031</v>
       </c>
       <c r="C2" t="n">
         <v>18.73409805461588</v>
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02302095899358392</v>
+        <v>0.02236025000456721</v>
       </c>
       <c r="C2" t="n">
         <v>26.02565028429637</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02723020798293874</v>
+        <v>0.02639541699318215</v>
       </c>
       <c r="C2" t="n">
         <v>24.38227002298181</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03069054201478139</v>
+        <v>0.02968791598686948</v>
       </c>
       <c r="C2" t="n">
         <v>32.08885103723333</v>
@@ -2111,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03495754196774215</v>
+        <v>0.03354954102542251</v>
       </c>
       <c r="C2" t="n">
         <v>20.50353872805189</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03219445800641552</v>
+        <v>0.03122183296363801</v>
       </c>
       <c r="C2" t="n">
         <v>25.36482630921306</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03194479201920331</v>
+        <v>0.03072525002062321</v>
       </c>
       <c r="C2" t="n">
         <v>23.45062215318757</v>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03282795799896121</v>
+        <v>0.03181895799934864</v>
       </c>
       <c r="C2" t="n">
         <v>24.52573028442807</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0335139170056209</v>
+        <v>0.03293145797215402</v>
       </c>
       <c r="C2" t="n">
         <v>22.86975966484743</v>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02694404195062816</v>
+        <v>0.02693495899438858</v>
       </c>
       <c r="C2" t="n">
         <v>25.13738544123525</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02671745896805078</v>
+        <v>0.02664383297087625</v>
       </c>
       <c r="C2" t="n">
         <v>23.20080774286751</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02767575002508238</v>
+        <v>0.02751345897559077</v>
       </c>
       <c r="C2" t="n">
         <v>26.22218971393179</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02641037496505305</v>
+        <v>0.0259280419559218</v>
       </c>
       <c r="C2" t="n">
         <v>22.93492273361795</v>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02157820895081386</v>
+        <v>0.02118537499336526</v>
       </c>
       <c r="C2" t="n">
         <v>31.92393684484261</v>
@@ -2851,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03634083300130442</v>
+        <v>0.03646637499332428</v>
       </c>
       <c r="C2" t="n">
         <v>25.38541693417424</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02890108403516933</v>
+        <v>0.02798487496329471</v>
       </c>
       <c r="C2" t="n">
         <v>26.86786396688949</v>
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02717583300545812</v>
+        <v>0.02660954103339463</v>
       </c>
       <c r="C2" t="n">
         <v>24.89669157078036</v>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02787900000112131</v>
+        <v>0.02765812497818843</v>
       </c>
       <c r="C2" t="n">
         <v>24.5204623764705</v>
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02636424999218434</v>
+        <v>0.0257404160220176</v>
       </c>
       <c r="C2" t="n">
         <v>20.99581656525724</v>
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02389308396959677</v>
+        <v>0.02317608403973281</v>
       </c>
       <c r="C2" t="n">
         <v>21.67636045466013</v>
@@ -3295,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03636566700879484</v>
+        <v>0.03507179202279076</v>
       </c>
       <c r="C2" t="n">
         <v>27.16000058096292</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02737920900108293</v>
+        <v>0.02633300004526973</v>
       </c>
       <c r="C2" t="n">
         <v>23.32450519552776</v>
@@ -3443,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03434175002621487</v>
+        <v>0.03336937498534098</v>
       </c>
       <c r="C2" t="n">
         <v>25.35499901546143</v>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03453499998431653</v>
+        <v>0.03379716700874269</v>
       </c>
       <c r="C2" t="n">
         <v>29.13691144454562</v>
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0291578330215998</v>
+        <v>0.02824916603276506</v>
       </c>
       <c r="C2" t="n">
         <v>24.06962159139147</v>
@@ -3665,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02303737500915304</v>
+        <v>0.02260154101531953</v>
       </c>
       <c r="C2" t="n">
         <v>22.63451409023795</v>
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02504216600209475</v>
+        <v>0.02481812500627711</v>
       </c>
       <c r="C2" t="n">
         <v>26.39145212338245</v>
@@ -3813,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03067704098066315</v>
+        <v>0.02965883305296302</v>
       </c>
       <c r="C2" t="n">
         <v>33.41689579957492</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03748912503942847</v>
+        <v>0.0366898329812102</v>
       </c>
       <c r="C2" t="n">
         <v>25.71800091586618</v>
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02558679197682068</v>
+        <v>0.02472883299924433</v>
       </c>
       <c r="C2" t="n">
         <v>27.29398089126719</v>
@@ -4035,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03374949999852106</v>
+        <v>0.03284212504513562</v>
       </c>
       <c r="C2" t="n">
         <v>27.48014656419171</v>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03130387497367337</v>
+        <v>0.03021104197250679</v>
       </c>
       <c r="C2" t="n">
         <v>34.47595901427077</v>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02922766702249646</v>
+        <v>0.02883354196092114</v>
       </c>
       <c r="C2" t="n">
         <v>25.98818249336412</v>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03636204195208848</v>
+        <v>0.03544066700851545</v>
       </c>
       <c r="C2" t="n">
         <v>28.42791459732292</v>
@@ -4331,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02905862499028444</v>
+        <v>0.02829062502132729</v>
       </c>
       <c r="C2" t="n">
         <v>24.98206023125813</v>
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02290879201609641</v>
+        <v>0.02254166599595919</v>
       </c>
       <c r="C2" t="n">
         <v>19.93444718920756</v>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02619174995925277</v>
+        <v>0.02496908296598122</v>
       </c>
       <c r="C2" t="n">
         <v>23.99197750921958</v>
@@ -4553,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03074633301002905</v>
+        <v>0.02951025002403185</v>
       </c>
       <c r="C2" t="n">
         <v>31.03815763859135</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03413541696500033</v>
+        <v>0.03315412497613579</v>
       </c>
       <c r="C2" t="n">
         <v>35.74724523320911</v>
@@ -4701,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03075808298308402</v>
+        <v>0.03016537497751415</v>
       </c>
       <c r="C2" t="n">
         <v>30.89408689257413</v>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0305797919863835</v>
+        <v>0.02980858297087252</v>
       </c>
       <c r="C2" t="n">
         <v>25.98910453436275</v>
@@ -4849,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0263309589936398</v>
+        <v>0.02632141701178625</v>
       </c>
       <c r="C2" t="n">
         <v>21.00373371382994</v>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03236550005385652</v>
+        <v>0.03124550002394244</v>
       </c>
       <c r="C2" t="n">
         <v>22.6080563668767</v>
@@ -4997,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0351290829712525</v>
+        <v>0.0353482500067912</v>
       </c>
       <c r="C2" t="n">
         <v>26.15951739047315</v>
@@ -5071,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03326012496836483</v>
+        <v>0.03266979096224532</v>
       </c>
       <c r="C2" t="n">
         <v>25.67628885769068</v>
@@ -5145,7 +5145,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03305979195283726</v>
+        <v>0.03210095799295232</v>
       </c>
       <c r="C2" t="n">
         <v>22.63202350637928</v>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03286204196047038</v>
+        <v>0.03255745803471655</v>
       </c>
       <c r="C2" t="n">
         <v>22.24889567344211</v>
@@ -5293,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03569275001063943</v>
+        <v>0.03469141601817682</v>
       </c>
       <c r="C2" t="n">
         <v>22.85569743005231</v>
@@ -5367,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03184591699391603</v>
+        <v>0.03123491600854322</v>
       </c>
       <c r="C2" t="n">
         <v>20.64704486733957</v>
@@ -5441,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03509329201187938</v>
+        <v>0.03407458297442645</v>
       </c>
       <c r="C2" t="n">
         <v>28.41226779144922</v>
@@ -5515,7 +5515,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03391974995611235</v>
+        <v>0.03299354098271579</v>
       </c>
       <c r="C2" t="n">
         <v>22.5269991510691</v>
@@ -5589,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02861037495313212</v>
+        <v>0.02799358399352059</v>
       </c>
       <c r="C2" t="n">
         <v>21.3707538209557</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02708570897812024</v>
+        <v>0.02627770899562165</v>
       </c>
       <c r="C2" t="n">
         <v>30.54284598135029</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02370429097209126</v>
+        <v>0.02278250001836568</v>
       </c>
       <c r="C2" t="n">
         <v>21.89078756265211</v>
@@ -5811,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02699941699393094</v>
+        <v>0.02607899997383356</v>
       </c>
       <c r="C2" t="n">
         <v>24.48818260209151</v>
@@ -5885,7 +5885,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02571208297740668</v>
+        <v>0.02555354096693918</v>
       </c>
       <c r="C2" t="n">
         <v>25.89093501416193</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03269091597758234</v>
+        <v>0.03198129194788635</v>
       </c>
       <c r="C2" t="n">
         <v>22.86725112673928</v>
@@ -6033,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02859125001123175</v>
+        <v>0.027844957949128</v>
       </c>
       <c r="C2" t="n">
         <v>21.8785947319056</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02630416600732133</v>
+        <v>0.0252022499917075</v>
       </c>
       <c r="C2" t="n">
         <v>24.5122652266085</v>
@@ -6181,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03961891605285928</v>
+        <v>0.03819999995175749</v>
       </c>
       <c r="C2" t="n">
         <v>21.27898547044218</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02309099998092279</v>
+        <v>0.02236833301139995</v>
       </c>
       <c r="C2" t="n">
         <v>23.07259938431408</v>
@@ -6329,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02647320798132569</v>
+        <v>0.0258497089962475</v>
       </c>
       <c r="C2" t="n">
         <v>28.02649332410587</v>
@@ -6403,7 +6403,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03294850001111627</v>
+        <v>0.03280845802510157</v>
       </c>
       <c r="C2" t="n">
         <v>22.3616344624749</v>
@@ -6477,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03179162496235222</v>
+        <v>0.0313315829844214</v>
       </c>
       <c r="C2" t="n">
         <v>22.94800705241712</v>
@@ -6551,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02531883300980553</v>
+        <v>0.02482945797964931</v>
       </c>
       <c r="C2" t="n">
         <v>22.00543203847982</v>
@@ -6625,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02911587501876056</v>
+        <v>0.02820012503070757</v>
       </c>
       <c r="C2" t="n">
         <v>24.22909887221899</v>
@@ -6699,7 +6699,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02293670800281689</v>
+        <v>0.02222570800222456</v>
       </c>
       <c r="C2" t="n">
         <v>18.95994216800527</v>
@@ -6773,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02849870797945186</v>
+        <v>0.02820991701446474</v>
       </c>
       <c r="C2" t="n">
         <v>34.67521992875228</v>
@@ -6847,7 +6847,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02598824998131022</v>
+        <v>0.02530595799908042</v>
       </c>
       <c r="C2" t="n">
         <v>19.28093893430197</v>
@@ -6921,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02863604197045788</v>
+        <v>0.02782004099572077</v>
       </c>
       <c r="C2" t="n">
         <v>23.12620728300609</v>
@@ -6995,7 +6995,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02248341700760648</v>
+        <v>0.02197454200359061</v>
       </c>
       <c r="C2" t="n">
         <v>18.8511768926202</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02356975001748651</v>
+        <v>0.02292516600573435</v>
       </c>
       <c r="C2" t="n">
         <v>22.83152539592711</v>
@@ -7143,7 +7143,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02438262500800192</v>
+        <v>0.02470012503908947</v>
       </c>
       <c r="C2" t="n">
         <v>28.92478911700643</v>
@@ -7217,7 +7217,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03454854199662805</v>
+        <v>0.03383512498112395</v>
       </c>
       <c r="C2" t="n">
         <v>24.14298108290447</v>
@@ -7291,7 +7291,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03509745799237862</v>
+        <v>0.03474637499311939</v>
       </c>
       <c r="C2" t="n">
         <v>25.91173318760667</v>
@@ -7365,7 +7365,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03119908401276916</v>
+        <v>0.02993599994806573</v>
       </c>
       <c r="C2" t="n">
         <v>19.66272459226778</v>
@@ -7439,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03349183301907033</v>
+        <v>0.03242479200707749</v>
       </c>
       <c r="C2" t="n">
         <v>25.36746532198887</v>
@@ -7513,7 +7513,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02210862498031929</v>
+        <v>0.02142804197501391</v>
       </c>
       <c r="C2" t="n">
         <v>26.1489901731184</v>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02506874996470287</v>
+        <v>0.0244945419835858</v>
       </c>
       <c r="C2" t="n">
         <v>21.98470103715546</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02748954197159037</v>
+        <v>0.0267518749460578</v>
       </c>
       <c r="C2" t="n">
         <v>27.39709419292355</v>
@@ -7735,7 +7735,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03269070800160989</v>
+        <v>0.03209562500705943</v>
       </c>
       <c r="C2" t="n">
         <v>23.82375361261148</v>
@@ -7809,7 +7809,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0297209580312483</v>
+        <v>0.02926733298227191</v>
       </c>
       <c r="C2" t="n">
         <v>27.81086102869544</v>
@@ -7883,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0328241249662824</v>
+        <v>0.03194041701499373</v>
       </c>
       <c r="C2" t="n">
         <v>24.6276790307636</v>

--- a/results/greedy/UAVs5_GRID13/revenue/UAVs5_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs5_GRID13/revenue/UAVs5_GRID13_Greedy.xlsx
@@ -557,7 +557,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02296962501714006</v>
+        <v>0.02334924996830523</v>
       </c>
       <c r="C2" t="n">
         <v>20.45781421728963</v>
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02785950002726167</v>
+        <v>0.02768766699591652</v>
       </c>
       <c r="C2" t="n">
         <v>24.21082778502821</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02710983296856284</v>
+        <v>0.02720412501366809</v>
       </c>
       <c r="C2" t="n">
         <v>26.87304175582018</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03039020899450406</v>
+        <v>0.03054866701131687</v>
       </c>
       <c r="C2" t="n">
         <v>21.98602605756687</v>
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04430641699582338</v>
+        <v>0.04449166700942442</v>
       </c>
       <c r="C2" t="n">
         <v>30.64303103957917</v>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03335133299697191</v>
+        <v>0.0333838330116123</v>
       </c>
       <c r="C2" t="n">
         <v>29.67441391729876</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02997954201418906</v>
+        <v>0.03027587500400841</v>
       </c>
       <c r="C2" t="n">
         <v>24.79311739002188</v>
@@ -1075,7 +1075,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03344879200449213</v>
+        <v>0.03412612498505041</v>
       </c>
       <c r="C2" t="n">
         <v>26.0120082395282</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0259322079946287</v>
+        <v>0.025954750017263</v>
       </c>
       <c r="C2" t="n">
         <v>24.10598692034544</v>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02525433403206989</v>
+        <v>0.0249991660239175</v>
       </c>
       <c r="C2" t="n">
         <v>27.54208785664958</v>
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02852349996101111</v>
+        <v>0.02846295799827203</v>
       </c>
       <c r="C2" t="n">
         <v>32.12246092247315</v>
@@ -1371,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0293934170040302</v>
+        <v>0.02895370800979435</v>
       </c>
       <c r="C2" t="n">
         <v>24.53157304962176</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02698595798574388</v>
+        <v>0.02756562503054738</v>
       </c>
       <c r="C2" t="n">
         <v>21.37485198136912</v>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03562583401799202</v>
+        <v>0.03514316596556455</v>
       </c>
       <c r="C2" t="n">
         <v>26.02678542891199</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02830870798788965</v>
+        <v>0.02817020803922787</v>
       </c>
       <c r="C2" t="n">
         <v>20.35028790612021</v>
@@ -1667,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02691191696794704</v>
+        <v>0.0270781249855645</v>
       </c>
       <c r="C2" t="n">
         <v>21.64598371852564</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0337352910428308</v>
+        <v>0.03318216599291191</v>
       </c>
       <c r="C2" t="n">
         <v>24.87876843618622</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02387729199836031</v>
+        <v>0.02396137500181794</v>
       </c>
       <c r="C2" t="n">
         <v>18.73409805461588</v>
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02236025000456721</v>
+        <v>0.02251245797378942</v>
       </c>
       <c r="C2" t="n">
         <v>26.02565028429637</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02639541699318215</v>
+        <v>0.02659429202321917</v>
       </c>
       <c r="C2" t="n">
         <v>24.38227002298181</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02968791598686948</v>
+        <v>0.02957787498598918</v>
       </c>
       <c r="C2" t="n">
         <v>32.08885103723333</v>
@@ -2111,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03354954102542251</v>
+        <v>0.03437370801111683</v>
       </c>
       <c r="C2" t="n">
         <v>20.50353872805189</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03122183296363801</v>
+        <v>0.03107999998610467</v>
       </c>
       <c r="C2" t="n">
         <v>25.36482630921306</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03072525002062321</v>
+        <v>0.03099858295172453</v>
       </c>
       <c r="C2" t="n">
         <v>23.45062215318757</v>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03181895799934864</v>
+        <v>0.03199245798168704</v>
       </c>
       <c r="C2" t="n">
         <v>24.52573028442807</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03293145797215402</v>
+        <v>0.03284904098836705</v>
       </c>
       <c r="C2" t="n">
         <v>22.86975966484743</v>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02693495899438858</v>
+        <v>0.02613483398454264</v>
       </c>
       <c r="C2" t="n">
         <v>25.13738544123525</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02664383297087625</v>
+        <v>0.02586820797296241</v>
       </c>
       <c r="C2" t="n">
         <v>23.20080774286751</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02751345897559077</v>
+        <v>0.02678812498925254</v>
       </c>
       <c r="C2" t="n">
         <v>26.22218971393179</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0259280419559218</v>
+        <v>0.02551549999043345</v>
       </c>
       <c r="C2" t="n">
         <v>22.93492273361795</v>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02118537499336526</v>
+        <v>0.02099370898213238</v>
       </c>
       <c r="C2" t="n">
         <v>31.92393684484261</v>
@@ -2851,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03646637499332428</v>
+        <v>0.03617691603722051</v>
       </c>
       <c r="C2" t="n">
         <v>25.38541693417424</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02798487496329471</v>
+        <v>0.02817895798943937</v>
       </c>
       <c r="C2" t="n">
         <v>26.86786396688949</v>
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02660954103339463</v>
+        <v>0.02668345900019631</v>
       </c>
       <c r="C2" t="n">
         <v>24.89669157078036</v>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02765812497818843</v>
+        <v>0.02751074999105185</v>
       </c>
       <c r="C2" t="n">
         <v>24.5204623764705</v>
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0257404160220176</v>
+        <v>0.0259312919806689</v>
       </c>
       <c r="C2" t="n">
         <v>20.99581656525724</v>
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02317608403973281</v>
+        <v>0.02318629197543487</v>
       </c>
       <c r="C2" t="n">
         <v>21.67636045466013</v>
@@ -3295,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03507179202279076</v>
+        <v>0.03577145800227299</v>
       </c>
       <c r="C2" t="n">
         <v>27.16000058096292</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02633300004526973</v>
+        <v>0.02668816701043397</v>
       </c>
       <c r="C2" t="n">
         <v>23.32450519552776</v>
@@ -3443,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03336937498534098</v>
+        <v>0.03331216605147347</v>
       </c>
       <c r="C2" t="n">
         <v>25.35499901546143</v>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03379716700874269</v>
+        <v>0.03352708299644291</v>
       </c>
       <c r="C2" t="n">
         <v>29.13691144454562</v>
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02824916603276506</v>
+        <v>0.02840387501055375</v>
       </c>
       <c r="C2" t="n">
         <v>24.06962159139147</v>
@@ -3665,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02260154101531953</v>
+        <v>0.02263079100521281</v>
       </c>
       <c r="C2" t="n">
         <v>22.63451409023795</v>
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02481812500627711</v>
+        <v>0.02488670800812542</v>
       </c>
       <c r="C2" t="n">
         <v>26.39145212338245</v>
@@ -3813,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02965883305296302</v>
+        <v>0.030069625005126</v>
       </c>
       <c r="C2" t="n">
         <v>33.41689579957492</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0366898329812102</v>
+        <v>0.03590216703014448</v>
       </c>
       <c r="C2" t="n">
         <v>25.71800091586618</v>
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02472883299924433</v>
+        <v>0.02478358300868422</v>
       </c>
       <c r="C2" t="n">
         <v>27.29398089126719</v>
@@ -4035,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03284212504513562</v>
+        <v>0.03323620901210234</v>
       </c>
       <c r="C2" t="n">
         <v>27.48014656419171</v>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03021104197250679</v>
+        <v>0.0306281250086613</v>
       </c>
       <c r="C2" t="n">
         <v>34.47595901427077</v>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02883354196092114</v>
+        <v>0.02881450002314523</v>
       </c>
       <c r="C2" t="n">
         <v>25.98818249336412</v>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03544066700851545</v>
+        <v>0.03581816703081131</v>
       </c>
       <c r="C2" t="n">
         <v>28.42791459732292</v>
@@ -4331,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02829062502132729</v>
+        <v>0.0287592500098981</v>
       </c>
       <c r="C2" t="n">
         <v>24.98206023125813</v>
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02254166599595919</v>
+        <v>0.02234608394792303</v>
       </c>
       <c r="C2" t="n">
         <v>19.93444718920756</v>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02496908296598122</v>
+        <v>0.02563845796976238</v>
       </c>
       <c r="C2" t="n">
         <v>23.99197750921958</v>
@@ -4553,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02951025002403185</v>
+        <v>0.02968408295419067</v>
       </c>
       <c r="C2" t="n">
         <v>31.03815763859135</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03315412497613579</v>
+        <v>0.03351812501205131</v>
       </c>
       <c r="C2" t="n">
         <v>35.74724523320911</v>
@@ -4701,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03016537497751415</v>
+        <v>0.02973004203522578</v>
       </c>
       <c r="C2" t="n">
         <v>30.89408689257413</v>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02980858297087252</v>
+        <v>0.02973562496481463</v>
       </c>
       <c r="C2" t="n">
         <v>25.98910453436275</v>
@@ -4849,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02632141701178625</v>
+        <v>0.02613958297297359</v>
       </c>
       <c r="C2" t="n">
         <v>21.00373371382994</v>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03124550002394244</v>
+        <v>0.03147854097187519</v>
       </c>
       <c r="C2" t="n">
         <v>22.6080563668767</v>
@@ -4997,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0353482500067912</v>
+        <v>0.03498774999752641</v>
       </c>
       <c r="C2" t="n">
         <v>26.15951739047315</v>
@@ -5071,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03266979096224532</v>
+        <v>0.032430374994874</v>
       </c>
       <c r="C2" t="n">
         <v>25.67628885769068</v>
@@ -5145,7 +5145,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03210095799295232</v>
+        <v>0.03255479200743139</v>
       </c>
       <c r="C2" t="n">
         <v>22.63202350637928</v>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03255745803471655</v>
+        <v>0.03240995900705457</v>
       </c>
       <c r="C2" t="n">
         <v>22.24889567344211</v>
@@ -5293,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03469141601817682</v>
+        <v>0.03474683302920312</v>
       </c>
       <c r="C2" t="n">
         <v>22.85569743005231</v>
@@ -5367,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03123491600854322</v>
+        <v>0.03107199998339638</v>
       </c>
       <c r="C2" t="n">
         <v>20.64704486733957</v>
@@ -5441,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03407458297442645</v>
+        <v>0.03415349998977035</v>
       </c>
       <c r="C2" t="n">
         <v>28.41226779144922</v>
@@ -5515,7 +5515,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03299354098271579</v>
+        <v>0.03335691697429866</v>
       </c>
       <c r="C2" t="n">
         <v>22.5269991510691</v>
@@ -5589,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02799358399352059</v>
+        <v>0.02795733301900327</v>
       </c>
       <c r="C2" t="n">
         <v>21.3707538209557</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02627770899562165</v>
+        <v>0.02666408300865442</v>
       </c>
       <c r="C2" t="n">
         <v>30.54284598135029</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02278250001836568</v>
+        <v>0.02321545901941136</v>
       </c>
       <c r="C2" t="n">
         <v>21.89078756265211</v>
@@ -5811,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02607899997383356</v>
+        <v>0.02621529099997133</v>
       </c>
       <c r="C2" t="n">
         <v>24.48818260209151</v>
@@ -5885,7 +5885,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02555354096693918</v>
+        <v>0.02538320800522342</v>
       </c>
       <c r="C2" t="n">
         <v>25.89093501416193</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03198129194788635</v>
+        <v>0.03153208398725837</v>
       </c>
       <c r="C2" t="n">
         <v>22.86725112673928</v>
@@ -6033,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.027844957949128</v>
+        <v>0.02798204100690782</v>
       </c>
       <c r="C2" t="n">
         <v>21.8785947319056</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0252022499917075</v>
+        <v>0.02540325000882149</v>
       </c>
       <c r="C2" t="n">
         <v>24.5122652266085</v>
@@ -6181,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03819999995175749</v>
+        <v>0.03855708299670368</v>
       </c>
       <c r="C2" t="n">
         <v>21.27898547044218</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02236833301139995</v>
+        <v>0.02246200002264231</v>
       </c>
       <c r="C2" t="n">
         <v>23.07259938431408</v>
@@ -6329,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0258497089962475</v>
+        <v>0.02585000003455207</v>
       </c>
       <c r="C2" t="n">
         <v>28.02649332410587</v>
@@ -6403,7 +6403,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03280845802510157</v>
+        <v>0.03260045900242403</v>
       </c>
       <c r="C2" t="n">
         <v>22.3616344624749</v>
@@ -6477,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0313315829844214</v>
+        <v>0.03113908402156085</v>
       </c>
       <c r="C2" t="n">
         <v>22.94800705241712</v>
@@ -6551,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02482945797964931</v>
+        <v>0.02476054197177291</v>
       </c>
       <c r="C2" t="n">
         <v>22.00543203847982</v>
@@ -6625,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02820012503070757</v>
+        <v>0.02847537497291341</v>
       </c>
       <c r="C2" t="n">
         <v>24.22909887221899</v>
@@ -6699,7 +6699,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02222570800222456</v>
+        <v>0.02224458300042897</v>
       </c>
       <c r="C2" t="n">
         <v>18.95994216800527</v>
@@ -6773,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02820991701446474</v>
+        <v>0.02818387496517971</v>
       </c>
       <c r="C2" t="n">
         <v>34.67521992875228</v>
@@ -6847,7 +6847,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02530595799908042</v>
+        <v>0.02532600000267848</v>
       </c>
       <c r="C2" t="n">
         <v>19.28093893430197</v>
@@ -6921,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02782004099572077</v>
+        <v>0.02790250000543892</v>
       </c>
       <c r="C2" t="n">
         <v>23.12620728300609</v>
@@ -6995,7 +6995,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02197454200359061</v>
+        <v>0.02204266702756286</v>
       </c>
       <c r="C2" t="n">
         <v>18.8511768926202</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02292516600573435</v>
+        <v>0.02311270800419152</v>
       </c>
       <c r="C2" t="n">
         <v>22.83152539592711</v>
@@ -7143,7 +7143,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02470012503908947</v>
+        <v>0.02368883299641311</v>
       </c>
       <c r="C2" t="n">
         <v>28.92478911700643</v>
@@ -7217,7 +7217,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03383512498112395</v>
+        <v>0.03394699998898432</v>
       </c>
       <c r="C2" t="n">
         <v>24.14298108290447</v>
@@ -7291,7 +7291,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03474637499311939</v>
+        <v>0.03464699996402487</v>
       </c>
       <c r="C2" t="n">
         <v>25.91173318760667</v>
@@ -7365,7 +7365,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02993599994806573</v>
+        <v>0.03029370802687481</v>
       </c>
       <c r="C2" t="n">
         <v>19.66272459226778</v>
@@ -7439,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03242479200707749</v>
+        <v>0.03281933401012793</v>
       </c>
       <c r="C2" t="n">
         <v>25.36746532198887</v>
@@ -7513,7 +7513,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02142804197501391</v>
+        <v>0.02162862499244511</v>
       </c>
       <c r="C2" t="n">
         <v>26.1489901731184</v>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0244945419835858</v>
+        <v>0.02472941600717604</v>
       </c>
       <c r="C2" t="n">
         <v>21.98470103715546</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0267518749460578</v>
+        <v>0.02711720898514614</v>
       </c>
       <c r="C2" t="n">
         <v>27.39709419292355</v>
@@ -7735,7 +7735,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03209562500705943</v>
+        <v>0.03199595800833777</v>
       </c>
       <c r="C2" t="n">
         <v>23.82375361261148</v>
@@ -7809,7 +7809,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02926733298227191</v>
+        <v>0.0294174169539474</v>
       </c>
       <c r="C2" t="n">
         <v>27.81086102869544</v>
@@ -7883,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03194041701499373</v>
+        <v>0.03234491701005027</v>
       </c>
       <c r="C2" t="n">
         <v>24.6276790307636</v>
